--- a/daily_matches/job_matches_2026-03-16.xlsx
+++ b/daily_matches/job_matches_2026-03-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,315 +468,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Senior Data Engineer &amp; Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Glue, Redshift, BigQuery, Synapse, Kinesis, CI/CD, Jenkins, Terraform, Git</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Kinesis, Snowflake, BigQuery, Redshift, Kafka, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a6b6e514fcadd1</t>
+          <t>https://www.indeed.com/viewjob?jk=6fd769b82cca737f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
+          <t>EverCommerce - Sr. BI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>11.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Keras, Docker, AKS</t>
+          <t>Data Lake, Hadoop, Tableau, Power BI, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fecf1fa5246a7b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Sr Forward Deployed Engineer</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Cayuse Holdings</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Data Lake, Docker, Kubernetes, CI/CD, NoSQL</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4c2d3ad3416a7e26</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AI &amp; Machine Learning Engineering Consultant - Life Sciences Sector - Senior - Consulting</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>EY</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, PyTorch, AKS, CI/CD, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=230bad3331a7b81d</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Senior AI Developer</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=957889215a16d70d</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Backend Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ClearlyRated</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>BigQuery, Dataflow, Kubernetes, CI/CD, Snowflake, BigQuery, Kafka, PostgreSQL, MySQL, SQL</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6018dcbcbcb04a3e</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>AI/ML Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ClearlyRated</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Pinecone, Prompt Engineering, GCP Vertex AI, Kafka, MongoDB, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5280bdd9d1f765d3</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior Agentic AI Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Icanio Technologies Inc</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, Prompt Engineering, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=308ad382c7e741a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Advanced Data Scientist</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Honeywell</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, Git, Python, R, Optimization, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ffb8646e3e7ed06</t>
+          <t>https://www.indeed.com/viewjob?jk=96fcb774adfa1d8f</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-16.xlsx
+++ b/daily_matches/job_matches_2026-03-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer &amp; Architect</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Sun Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Kinesis, Snowflake, BigQuery, Redshift, Kafka, Python</t>
+          <t>Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,42 +496,112 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fd769b82cca737f</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e43a65f53e347c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EverCommerce - Sr. BI Engineer</t>
+          <t>Software Engineer II - Data / ETL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Lake, Hadoop, Tableau, Power BI, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, CI/CD, Jenkins, Terraform, Git, Snowflake, Databricks, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96fcb774adfa1d8f</t>
+          <t>https://www.indeed.com/viewjob?jk=ec636208e5ebd53d</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TEEMA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5357891576d1cc2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TEEMA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c83697ea95747beb</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-16.xlsx
+++ b/daily_matches/job_matches_2026-03-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Identity AI / ML Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sun Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, AKS, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1e43a65f53e347c</t>
+          <t>https://www.indeed.com/viewjob?jk=cc5cbe3f87597ff3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer II - Data / ETL</t>
+          <t>Network Operations Trainee</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, Terraform, Git, Snowflake, Databricks, NoSQL, Python, SQL</t>
+          <t>MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, Cassandra, Tableau</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,77 +531,392 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec636208e5ebd53d</t>
+          <t>https://www.indeed.com/viewjob?jk=88bda3516bc06812</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, PyTorch, Azure ML, Synapse, MLflow, Kubernetes, AKS, Databricks, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5357891576d1cc2a</t>
+          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Identity AI / ML Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, S3, EC2, Glue, Athena, Terraform, Python</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b2285059f147509</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sr. Data Analyst</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Optimum</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cbfe0b36ac903273</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sr. Data Analyst</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Optimum</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Long Island City, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1dd26c27b17290d</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sr. Data Analyst</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Optimum</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bethpage, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a69d3f0aa1e396b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Big Data Engineer - AWS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Purple Austyn Technologies</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Rockville, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>S3, Glue, Athena, Data Lake, Kubernetes, CI/CD, Jenkins, Hadoop, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=943257051095e0f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Identity AI / ML Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=024266089b9b0fb7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Menlo Park, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Data Scientist, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c28f65d796e1a52b</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AI Model Deployment Administrator</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, FAISS, Pinecone, Prompt Engineering, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c85e8921c47dfab</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Identity AI / ML Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>10</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c83697ea95747beb</t>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87f070d9bd7d1344</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Machine Learning</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Dhara Consulting Group</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d65283af914e6892</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-16.xlsx
+++ b/daily_matches/job_matches_2026-03-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>Software Engineer III - Backend/Java</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, AKS, GitHub Actions, Terraform, Git</t>
+          <t>RAG, Copilot, S3, Kinesis, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc5cbe3f87597ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=6c1fd07d72b779f4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Network Operations Trainee</t>
+          <t>Software Engineer III - SDET</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, Cassandra, Tableau</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88bda3516bc06812</t>
+          <t>https://www.indeed.com/viewjob?jk=95c7d23da1d85f79</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
+          <t>(1383) Senior SRE/DevOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Nearsure</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, PyTorch, Azure ML, Synapse, MLflow, Kubernetes, AKS, Databricks, Python</t>
+          <t>Generative AI, EC2, Docker, AKS, Jenkins, Terraform, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
+          <t>https://www.indeed.com/viewjob?jk=8598ff2a82d03277</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>Senior AI/ML Engineer Voice Bots - Remote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, S3, EC2, Glue, Athena, Terraform, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, CI/CD, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b2285059f147509</t>
+          <t>https://www.indeed.com/viewjob?jk=e6dcf2209323dbf3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst</t>
+          <t>AI Architect– Insurance (Mandatory) | Azure | API-First Microservices (.NET Program)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>Tms Llc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Tableau, Power BI, Python</t>
+          <t>AI Engineer, Data Scientist, Docker, Kubernetes, AKS, CI/CD, Kafka, R, Optimization</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,287 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfe0b36ac903273</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Sr. Data Analyst</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Optimum</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Long Island City, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Tableau, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1dd26c27b17290d</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Sr. Data Analyst</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Optimum</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bethpage, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Tableau, Power BI, Python</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a69d3f0aa1e396b4</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior Big Data Engineer - AWS</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Purple Austyn Technologies</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Rockville, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>S3, Glue, Athena, Data Lake, Kubernetes, CI/CD, Jenkins, Hadoop, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=943257051095e0f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Identity AI / ML Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=024266089b9b0fb7</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Menlo Park, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Data Scientist, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c28f65d796e1a52b</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>AI Model Deployment Administrator</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, FAISS, Pinecone, Prompt Engineering, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6c85e8921c47dfab</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Identity AI / ML Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=87f070d9bd7d1344</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Machine Learning</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Dhara Consulting Group</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d65283af914e6892</t>
+          <t>https://www.indeed.com/viewjob?jk=6fe778887727f0be</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-16.xlsx
+++ b/daily_matches/job_matches_2026-03-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer III - Backend/Java</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Kinesis, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka</t>
+          <t>RAG, TensorFlow, PyTorch, S3, FastAPI, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c1fd07d72b779f4</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d1545b725cacf9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III - SDET</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RAG, TensorFlow, PyTorch, S3, FastAPI, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95c7d23da1d85f79</t>
+          <t>https://www.indeed.com/viewjob?jk=6e62fa620ec25df7</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>(1383) Senior SRE/DevOps Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nearsure</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, EC2, Docker, AKS, Jenkins, Terraform, Git, NoSQL, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Hugging Face, Azure ML, Synapse, Data Lake, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8598ff2a82d03277</t>
+          <t>https://www.indeed.com/viewjob?jk=4181653d522a2852</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer Voice Bots - Remote</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, CI/CD, Git, Python, R, Scala, Optimization</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, FAISS, Pinecone</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,42 +601,1022 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6dcf2209323dbf3</t>
+          <t>https://www.indeed.com/viewjob?jk=078f5640bcaf4456</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Architect– Insurance (Mandatory) | Azure | API-First Microservices (.NET Program)</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tms Llc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, LLaMA, TensorFlow, PyTorch, XGBoost, Docker, Tableau, Power BI, Matplotlib</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d388abf305420b67</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Kubernetes MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>S3, Glue, Athena, Redshift, Kinesis, Docker, Kubernetes, CI/CD, Git, Redshift</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8674e111f05b66a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Associate ML Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, Cassandra, Tableau</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1527cf38b699a4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Generative AI Scientist</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Wabash Solutions</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, S3, FastAPI, Docker, Kubernetes, CI/CD, MongoDB, Python</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3ffa8e9cd961ff3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Azure ML, MLflow, Databricks</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70f47f4cc01cf8f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AI Model Deployment Administrator</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, S3, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e25459284392a1d</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Production Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Legion</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, MySQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8bdd4694bf19ea44</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Pricing Data Scientist</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Engage3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Lehi, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, S3, EC2, Git, Snowflake, PostgreSQL, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00e148dc9291d2a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Kubernetes MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, FAISS, Pinecone, FastAPI, Docker, Kubernetes, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b5f987d09c743c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Kafka</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Data Lake, Kinesis, CI/CD, Databricks, PySpark, Kafka, SQL, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Kafka</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, S3, Kubernetes, CI/CD, Jenkins, Git, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b70601a63d53974b</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Associate ML Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Snowflake, Kafka, MongoDB, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db5f1b4995387bfb</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Streaming Data</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Snowflake, Kafka, MongoDB, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8cefe5f8a541b23c</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Streaming Data</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Snowflake, Kafka, MongoDB, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba7766dd10fa7638</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>LLM Deployment Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14db0ddebb35193f</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Kafka API Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Generative AI, Docker, Kubernetes, Jenkins, Git, Kafka, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9dd2998e213ac80</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Agentic QA Engineer / Generative AI &amp; Agentic Systems (Contract &amp; FTE)-1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, LLaMA, CI/CD, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1be9eb9f66af3832</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Kubernetes MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=debbd827524fea88</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Kubernetes MLOps Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85ea190b4d6cfe84</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Associate ML Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Terraform, Git, Snowflake, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76acc9d073486515</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Google Cloud Network Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, Terraform, Git, Snowflake, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d574d83eecc2af8</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Software Engineer Specialists – Mortgage Solutions</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FIS</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>10</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Docker, Kubernetes, AKS, CI/CD, Kafka, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6fe778887727f0be</t>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e24122f1c8a5b1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7515ca35650e9a85</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Sr Full Stack Developer - HUB</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>DPR Construction</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Copilot, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef66cc37d4d3fe58</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Java Trainer / Mentor / Educator</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=540acf98f88d6845</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MLOps</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, SQL, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=acc51f463ee55f82</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MLOps</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Kubernetes, CI/CD, Jenkins, Git, Kafka, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Kafka Administrator</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Kubernetes, CI/CD, Jenkins, Git, Kafka, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>IAM Administrator</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Prompt Engineering, S3, EC2, CI/CD, Terraform, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ae0dd5ea1f55fbcc</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-16.xlsx
+++ b/daily_matches/job_matches_2026-03-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Sr AI/ML Engineer - Hybrid in MN or DC - Remote elsewhere</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, S3, FastAPI, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Hugging Face, Prompt Engineering, TensorFlow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d1545b725cacf9</t>
+          <t>https://www.indeed.com/viewjob?jk=1e711b1143e9a946</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>IT Systems Engineer - Linux/Platform Operations</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JMA Wireless</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, S3, FastAPI, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e62fa620ec25df7</t>
+          <t>https://www.indeed.com/viewjob?jk=0c45683c60eeacd5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Hugging Face, Azure ML, Synapse, Data Lake, MLflow, CI/CD</t>
+          <t>RAG, Docker, AKS, CI/CD, GitHub Actions, Terraform, Git, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4181653d522a2852</t>
+          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, FAISS, Pinecone</t>
+          <t>RAG, Docker, AKS, CI/CD, GitHub Actions, Terraform, Git, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=078f5640bcaf4456</t>
+          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Akamai</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, LLaMA, TensorFlow, PyTorch, XGBoost, Docker, Tableau, Power BI, Matplotlib</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, Git, PostgreSQL, Cassandra, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d388abf305420b67</t>
+          <t>https://www.indeed.com/viewjob?jk=f119c4f4124a7784</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Litera</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S3, Glue, Athena, Redshift, Kinesis, Docker, Kubernetes, CI/CD, Git, Redshift</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8674e111f05b66a1</t>
+          <t>https://www.indeed.com/viewjob?jk=53f842184f1c8907</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Senior Backend Java Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Inmar</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, Cassandra, Tableau</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1527cf38b699a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=ff39e4caa2d9b921</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Generative AI Scientist</t>
+          <t>(USA) Data Scientist III</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wabash Solutions</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, S3, FastAPI, Docker, Kubernetes, CI/CD, MongoDB, Python</t>
+          <t>Data Scientist, RAG, TensorFlow, BigQuery, Git, BigQuery, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3ffa8e9cd961ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=64c779a8ad7c2bd4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Qb Energy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Azure ML, MLflow, Databricks</t>
+          <t>Copilot, BigQuery, FastAPI, Git, Snowflake, BigQuery, PostgreSQL, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70f47f4cc01cf8f2</t>
+          <t>https://www.indeed.com/viewjob?jk=3b91c5ea25135770</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Model Deployment Administrator</t>
+          <t>Research Software Engineer – Clinical NLP (Data Science &amp; AI Institute)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Johns Hopkins University</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, S3, CI/CD, Python</t>
+          <t>AI Engineer, Data Scientist, RAG, Prompt Engineering, BioBERT, ClinicalBERT, Docker, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e25459284392a1d</t>
+          <t>https://www.indeed.com/viewjob?jk=947e4c10fea0b477</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Production Engineer</t>
+          <t>Security Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>Tebra</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, MySQL, Python, SQL</t>
+          <t>BigQuery, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bdd4694bf19ea44</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3f0014b8bc7264</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Pricing Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Engage3</t>
+          <t>Energyby5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, EC2, Git, Snowflake, PostgreSQL, Tableau, Python, SQL, R</t>
+          <t>RAG, Athena, Docker, CI/CD, GitHub Actions, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00e148dc9291d2a9</t>
+          <t>https://www.indeed.com/viewjob?jk=f5016f77a0e9f421</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Energyby5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, FAISS, Pinecone, FastAPI, Docker, Kubernetes, CI/CD, Python</t>
+          <t>RAG, Athena, Docker, CI/CD, GitHub Actions, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b5f987d09c743c1</t>
+          <t>https://www.indeed.com/viewjob?jk=4a5059671136ac6d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Data Scientist, Senior</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>State of Wisconsin Investment Board</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Kinesis, CI/CD, Databricks, PySpark, Kafka, SQL, R</t>
+          <t>Data Scientist, RAG, CI/CD, Terraform, Git, Snowflake, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
+          <t>https://www.indeed.com/viewjob?jk=997bc037bc65462b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, S3, Kubernetes, CI/CD, Jenkins, Git, Kafka, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b70601a63d53974b</t>
+          <t>https://www.indeed.com/viewjob?jk=ddcf5ba6b877da9f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Afresh</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Snowflake, Kafka, MongoDB, Python, SQL</t>
+          <t>RAG, Snowflake, Databricks, PySpark, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db5f1b4995387bfb</t>
+          <t>https://www.indeed.com/viewjob?jk=7af58a10e3799d7c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>LLM Evaluation Engineer / Generative AI Quality Engineer - W2 Only</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ACR Technology Inc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Snowflake, Kafka, MongoDB, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, CI/CD, PySpark, Python, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cefe5f8a541b23c</t>
+          <t>https://www.indeed.com/viewjob?jk=d7ea89b9d95bcf7f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Streaming Data</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, Snowflake, Kafka, MongoDB, Python, SQL</t>
+          <t>RAG, Kubernetes, Apache Airflow, CI/CD, Terraform, Kafka, Python, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba7766dd10fa7638</t>
+          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LLM Deployment Engineer</t>
+          <t>Sr. Software Engineer, Embedded AI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vivint</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
+          <t>OpenCV, Docker, Kubernetes, CI/CD, Git, Python, R, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14db0ddebb35193f</t>
+          <t>https://www.indeed.com/viewjob?jk=99452307c5066215</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kafka API Engineer</t>
+          <t>Senior Product Security Engineer - Applications</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optimum</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Generative AI, Docker, Kubernetes, Jenkins, Git, Kafka, NoSQL, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9dd2998e213ac80</t>
+          <t>https://www.indeed.com/viewjob?jk=6cd45de64e1029fc</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Agentic QA Engineer / Generative AI &amp; Agentic Systems (Contract &amp; FTE)-1</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, LLaMA, CI/CD, GitHub Actions, Git, Python, R, Java</t>
+          <t>Copilot, Prompt Engineering, TensorFlow, PyTorch, OpenCV, CI/CD, Python, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1be9eb9f66af3832</t>
+          <t>https://www.indeed.com/viewjob?jk=87af58a8c5e5b206</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Marketing Data Scientist</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, Git, Tableau, Python, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,392 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=debbd827524fea88</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Kubernetes MLOps Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=85ea190b4d6cfe84</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Associate ML Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, Terraform, Git, Snowflake, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=76acc9d073486515</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Google Cloud Network Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, Terraform, Git, Snowflake, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d574d83eecc2af8</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Software Engineer Specialists – Mortgage Solutions</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>FIS</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e24122f1c8a5b1a</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>AI/ML Engineer - Remote</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7515ca35650e9a85</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Sr Full Stack Developer - HUB</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>DPR Construction</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Copilot, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef66cc37d4d3fe58</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Java Trainer / Mentor / Educator</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=540acf98f88d6845</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>MLOps</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, SQL, R</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=acc51f463ee55f82</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>MLOps</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Kubernetes, CI/CD, Jenkins, Git, Kafka, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Kafka Administrator</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Kubernetes, CI/CD, Jenkins, Git, Kafka, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>IAM Administrator</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Prompt Engineering, S3, EC2, CI/CD, Terraform, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ae0dd5ea1f55fbcc</t>
+          <t>https://www.indeed.com/viewjob?jk=279c5a81473eb457</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-16.xlsx
+++ b/daily_matches/job_matches_2026-03-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr AI/ML Engineer - Hybrid in MN or DC - Remote elsewhere</t>
+          <t>Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Hugging Face, Prompt Engineering, TensorFlow</t>
+          <t>RAG, LLaMA, Gemini, Redshift, BigQuery, Data Lake, Docker, Kubernetes, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e711b1143e9a946</t>
+          <t>https://www.indeed.com/viewjob?jk=b36bcd88655ec26b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IT Systems Engineer - Linux/Platform Operations</t>
+          <t>Gen AI Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JMA Wireless</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, MySQL</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c45683c60eeacd5</t>
+          <t>https://www.indeed.com/viewjob?jk=773456aff3611238</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Software Engineer - TS/SCI with Polygraph</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, AKS, CI/CD, GitHub Actions, Terraform, Git, Power BI, Python, SQL</t>
+          <t>Data Scientist, Generative AI, S3, EC2, Docker, CI/CD, Jenkins, Terraform, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
+          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Python-AI_ML-GenAI- Senior Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, AKS, CI/CD, GitHub Actions, Terraform, Git, Power BI, Python, SQL</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Docker, CI/CD, Jenkins, Git, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
+          <t>https://www.indeed.com/viewjob?jk=7e2aee8ab70eada4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Fellow Software Engineer-Eng (Agentic AI Architecture &amp; Engineering)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Akamai</t>
+          <t>UKG</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, Git, PostgreSQL, Cassandra, NoSQL, Python, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f119c4f4124a7784</t>
+          <t>https://www.indeed.com/viewjob?jk=b6640f8a8e78faa9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Litera</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Git, PostgreSQL</t>
+          <t>AI Engineer, RAG, Prompt Engineering, Data Lake, CI/CD, Git, Databricks, PySpark, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f842184f1c8907</t>
+          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Backend Java Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Inmar</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, R</t>
+          <t>Data Scientist, S3, Glue, Athena, Redshift, Data Lake, CI/CD, Terraform, Redshift, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff39e4caa2d9b921</t>
+          <t>https://www.indeed.com/viewjob?jk=5861e377dbf3fbc8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>(USA) Data Scientist III</t>
+          <t>AI Engineering Coach</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Optwise Consulting</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, BigQuery, Git, BigQuery, Tableau, Power BI, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, FastAPI</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64c779a8ad7c2bd4</t>
+          <t>https://www.indeed.com/viewjob?jk=33e2823fa36cfde4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Qb Energy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Copilot, BigQuery, FastAPI, Git, Snowflake, BigQuery, PostgreSQL, Power BI, Python, SQL</t>
+          <t>AI Engineer, LangChain, RAG, EC2, FastAPI, Docker, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b91c5ea25135770</t>
+          <t>https://www.indeed.com/viewjob?jk=a150d5ba13681762</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Research Software Engineer – Clinical NLP (Data Science &amp; AI Institute)</t>
+          <t>Sr Software Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Johns Hopkins University</t>
+          <t>Xylem</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,52 +801,52 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Prompt Engineering, BioBERT, ClinicalBERT, Docker, Git, Databricks, Python</t>
+          <t>LangChain, LLaMA, CI/CD, Git, PostgreSQL, MongoDB, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947e4c10fea0b477</t>
+          <t>https://www.indeed.com/viewjob?jk=7bca75cc7f67ba36</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Security Architect</t>
+          <t>Senior Robotics Software Engineer (R&amp;D)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tebra</t>
+          <t>Prime Vision</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BigQuery, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, Python, SQL, R</t>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3f0014b8bc7264</t>
+          <t>https://www.indeed.com/viewjob?jk=d33bc6eb54ac8145</t>
         </is>
       </c>
     </row>
@@ -858,20 +858,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Energyby5</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Athena, Docker, CI/CD, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5016f77a0e9f421</t>
+          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Machine Learning Engineer - Generative AI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Energyby5</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Athena, Docker, CI/CD, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a5059671136ac6d</t>
+          <t>https://www.indeed.com/viewjob?jk=51efb2c8a7f587c4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Scientist, Senior</t>
+          <t>Backend Developer - .NET &amp; Azure</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>State of Wisconsin Investment Board</t>
+          <t>Reidy</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Terraform, Git, Snowflake, Power BI, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=997bc037bc65462b</t>
+          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior SDET - Performance Test Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CyberArk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kafka, Python, SQL, R</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddcf5ba6b877da9f</t>
+          <t>https://www.indeed.com/viewjob?jk=64e75a054f0e88a5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>REFRAME Full Stack Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Afresh</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Snowflake, Databricks, PySpark, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7af58a10e3799d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=9a83cc2c75866e85</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LLM Evaluation Engineer / Generative AI Quality Engineer - W2 Only</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ACR Technology Inc</t>
+          <t>MANTECH</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, CI/CD, PySpark, Python, R</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, R, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7ea89b9d95bcf7f</t>
+          <t>https://www.indeed.com/viewjob?jk=a3242ebfcbbd1221</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>AI &amp; Automation Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>RectorSeal</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Apache Airflow, CI/CD, Terraform, Kafka, Python, R, Scala</t>
+          <t>RAG, Azure ML, CI/CD, Git, Python, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=38ee25a7ad5dfec4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Embedded AI</t>
+          <t>IOT Developer - 4.0 Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vivint</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>OpenCV, Docker, Kubernetes, CI/CD, Git, Python, R, Optimization, A/B Testing</t>
+          <t>RAG, MySQL, NoSQL, Power BI, Quicksight, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99452307c5066215</t>
+          <t>https://www.indeed.com/viewjob?jk=05bfdedaaaf8d704</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Product Security Engineer - Applications</t>
+          <t>Intern, Software Engineering - Summer Internship</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>Gen</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Git, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd45de64e1029fc</t>
+          <t>https://www.indeed.com/viewjob?jk=5b469568946c6370</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Java-Python-Senior Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Copilot, Prompt Engineering, TensorFlow, PyTorch, OpenCV, CI/CD, Python, R, Scala</t>
+          <t>CI/CD, Jenkins, Git, Kafka, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87af58a8c5e5b206</t>
+          <t>https://www.indeed.com/viewjob?jk=915d06b7ed7b70f8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marketing Data Scientist</t>
+          <t>CCaaS-Five9-GCP-Senior Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Tableau, Python, SQL, R, Java, Optimization</t>
+          <t>RAG, BigQuery, CI/CD, GitHub Actions, Terraform, Git, BigQuery, R, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,77 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=279c5a81473eb457</t>
+          <t>https://www.indeed.com/viewjob?jk=7acb32c3f39a2f02</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Commercial Operations BI Analyst</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Colgate-Palmolive</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Piscataway, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Snowflake, BigQuery, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DevOps Engineering Scientist</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>University of Texas at Austin</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b24bafca3041febf</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-16.xlsx
+++ b/daily_matches/job_matches_2026-03-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer (Remote)</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, Gemini, Redshift, BigQuery, Data Lake, Docker, Kubernetes, Apache Airflow, Git</t>
+          <t>RAG, TensorFlow, PyTorch, S3, FastAPI, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36bcd88655ec26b</t>
+          <t>https://www.indeed.com/viewjob?jk=b271d311d5d546b6</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gen AI Developer</t>
+          <t>AI Industry 5.0 Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Bloom Energy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>Data Scientist, TensorFlow, PyTorch, Keras, Docker, Kubernetes, CI/CD, Git, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=773456aff3611238</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd1a549fc1388c4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer - TS/SCI with Polygraph</t>
+          <t>Senior Software and Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, S3, EC2, Docker, CI/CD, Jenkins, Terraform, Git, PostgreSQL</t>
+          <t>Data Scientist, RAG, S3, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
+          <t>https://www.indeed.com/viewjob?jk=dfe225f990f2b49a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Python-AI_ML-GenAI- Senior Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Docker, CI/CD, Jenkins, Git, Kafka</t>
+          <t>RAG, Copilot, Kinesis, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e2aee8ab70eada4</t>
+          <t>https://www.indeed.com/viewjob?jk=3b873d81ef6e6821</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Fellow Software Engineer-Eng (Agentic AI Architecture &amp; Engineering)</t>
+          <t>Application Developer Sr II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UKG</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>Data Scientist, RAG, S3, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6640f8a8e78faa9</t>
+          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Software Engineer/Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Valor</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Data Lake, CI/CD, Git, Databricks, PySpark, Tableau, Power BI</t>
+          <t>RAG, Gemini, CI/CD, GitHub Actions, Git, Snowflake, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
+          <t>https://www.indeed.com/viewjob?jk=2395d8e4009e6898</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, Glue, Athena, Redshift, Data Lake, CI/CD, Terraform, Redshift, PySpark</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5861e377dbf3fbc8</t>
+          <t>https://www.indeed.com/viewjob?jk=924e73b21b6d445b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Engineering Coach</t>
+          <t>Application Developer Sr I</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Optwise Consulting</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, FastAPI</t>
+          <t>RAG, S3, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks, MySQL, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e2823fa36cfde4</t>
+          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
         </is>
       </c>
     </row>
@@ -753,20 +753,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Abbott Park, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, EC2, FastAPI, Docker, Git, PostgreSQL, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, RAG, TensorFlow, Git, PostgreSQL, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a150d5ba13681762</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f5dafb0b850ea1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Software Developer</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Xylem</t>
+          <t>Alteryx</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LangChain, LLaMA, CI/CD, Git, PostgreSQL, MongoDB, Python, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, Data Lake, Snowflake, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bca75cc7f67ba36</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a369f4875834d9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Robotics Software Engineer (R&amp;D)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Prime Vision</t>
+          <t>Alteryx</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, Python, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, Data Lake, Snowflake, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d33bc6eb54ac8145</t>
+          <t>https://www.indeed.com/viewjob?jk=335fd743bc261aa1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, SQL, R, Java</t>
+          <t>Generative AI, Docker, Kubernetes, Jenkins, Git, Kafka, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
+          <t>https://www.indeed.com/viewjob?jk=04be996b03ec5feb</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - Generative AI</t>
+          <t>Google Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python</t>
+          <t>RAG, CI/CD, Jenkins, Terraform, Git, Snowflake, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51efb2c8a7f587c4</t>
+          <t>https://www.indeed.com/viewjob?jk=ebc7e2129c884b1f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Backend Developer - .NET &amp; Azure</t>
+          <t>Internship, Machine Learning Engineer, Data Engineering &amp; Analytics (Summer 2026)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Reidy</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Docker, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
+          <t>https://www.indeed.com/viewjob?jk=0905aae82c59fcab</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior SDET - Performance Test Engineer</t>
+          <t>Information Systems Architect - Consultant</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CyberArk</t>
+          <t>DatamanUSA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Java, Scala</t>
+          <t>Prompt Engineering, S3, EC2, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e75a054f0e88a5</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4a2963fd5a1441</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>REFRAME Full Stack Developer</t>
+          <t>Sr. SW Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>Generative AI, Prompt Engineering, S3, Docker, Kubernetes, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a83cc2c75866e85</t>
+          <t>https://www.indeed.com/viewjob?jk=13374ce6b38e86b1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Kafka API Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MANTECH</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, R, Optimization</t>
+          <t>EC2, Docker, CI/CD, Git, Kafka, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3242ebfcbbd1221</t>
+          <t>https://www.indeed.com/viewjob?jk=161ce7550aeaef47</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI &amp; Automation Engineer (Hybrid)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RectorSeal</t>
+          <t>GitHub</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Azure ML, CI/CD, Git, Python, SQL, R, Java, Optimization</t>
+          <t>RAG, Copilot, CI/CD, Git, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ee25a7ad5dfec4</t>
+          <t>https://www.indeed.com/viewjob?jk=1e4396485f37b816</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IOT Developer - 4.0 Engineer</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Magna International</t>
+          <t>First Solar</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Perrysburg, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, MySQL, NoSQL, Power BI, Quicksight, Python, SQL, R, Java</t>
+          <t>TensorFlow, PyTorch, XGBoost, Keras, Tableau, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bfdedaaaf8d704</t>
+          <t>https://www.indeed.com/viewjob?jk=7be169bbf4e9b52b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Intern, Software Engineering - Summer Internship</t>
+          <t>Kafka Administrator</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Gen</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>Kubernetes, CI/CD, Jenkins, Git, Kafka, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b469568946c6370</t>
+          <t>https://www.indeed.com/viewjob?jk=d43be3a205ebe705</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Java-Python-Senior Engineer</t>
+          <t>Sr Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Birlasoft</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CI/CD, Jenkins, Git, Kafka, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, Docker, Kubernetes, Kafka, Hadoop, Tableau, Power BI, Python, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,112 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=915d06b7ed7b70f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>CCaaS-Five9-GCP-Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Objectways Technologies</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, CI/CD, GitHub Actions, Terraform, Git, BigQuery, R, Scala</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7acb32c3f39a2f02</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Commercial Operations BI Analyst</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Colgate-Palmolive</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Piscataway, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, Snowflake, BigQuery, Tableau, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>DevOps Engineering Scientist</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>University of Texas at Austin</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b24bafca3041febf</t>
+          <t>https://www.indeed.com/viewjob?jk=b61de9cae3cb1f9d</t>
         </is>
       </c>
     </row>
